--- a/astro-site/public/dl/restaurant-checklist-templates/04-daily-duties-side-work-by-role.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/04-daily-duties-side-work-by-role.xlsx
@@ -840,7 +840,7 @@
     <row r="28" ht="31" customHeight="1">
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
     <row r="32" ht="47" customHeight="1">
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>▸ You are in 04-daily-duties-side-work-by-role.xlsx: it is one MORE layer, not a repeat — the frame of the day is in 08-restaurant-opening-closing-checklist.xlsx and 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
+          <t>▸ You are in 04-daily-duties-side-work-by-role.xlsx: it is one MORE layer, not a repeat — the backbone of the day is in 08-restaurant-opening-closing-checklist.xlsx and 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
